--- a/Zinc/5. Statistical data analysis/Multiple linear regression/MLR.xlsx
+++ b/Zinc/5. Statistical data analysis/Multiple linear regression/MLR.xlsx
@@ -7,13 +7,12 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Omitting Na" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
@@ -30,55 +29,37 @@
     <t xml:space="preserve">Rel_Importance</t>
   </si>
   <si>
-    <t xml:space="preserve">log_Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Mg_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Na_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Temp_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std_Beta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_uM</t>
+    <t xml:space="preserve">log_Zn_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DOC_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Ca_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_DIC_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Cl_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Na_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Mg_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_K_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_Temp_C_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_SO4_nM_std</t>
   </si>
 </sst>
 </file>
@@ -429,16 +410,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.90905364793537</v>
+        <v>0.910695187765478</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000375256425259254</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000222900569542897</v>
       </c>
       <c r="D2" t="n">
-        <v>1.51976587358555</v>
+        <v>1.53536661428277</v>
       </c>
       <c r="E2" t="n">
-        <v>0.616053608293772</v>
+        <v>0.606975916550295</v>
       </c>
     </row>
     <row r="3">
@@ -446,16 +427,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.443184017220206</v>
+        <v>-0.433260775216521</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000222205803664535</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000262966983851638</v>
       </c>
       <c r="D3" t="n">
-        <v>3.61992827149766</v>
+        <v>2.52926565538351</v>
       </c>
       <c r="E3" t="n">
-        <v>0.138339111113914</v>
+        <v>0.114612427409943</v>
       </c>
     </row>
     <row r="4">
@@ -463,16 +444,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.430289904357391</v>
+        <v>-0.411414098168037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000119036493915239</v>
+        <v>0.000000000000000000000153137783708475</v>
       </c>
       <c r="D4" t="n">
-        <v>2.47816694773436</v>
+        <v>9.46344895045439</v>
       </c>
       <c r="E4" t="n">
-        <v>0.115848695035675</v>
+        <v>0.101805360926366</v>
       </c>
     </row>
     <row r="5">
@@ -480,16 +461,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0369000517856304</v>
+        <v>-0.039102431368606</v>
       </c>
       <c r="C5" t="n">
-        <v>0.161588605048648</v>
+        <v>0.305847867918413</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2129745633162</v>
+        <v>8.85217301490392</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0264307405305168</v>
+        <v>0.0499480437048786</v>
       </c>
     </row>
     <row r="6">
@@ -497,16 +478,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.179110025538271</v>
+        <v>-0.182943297124043</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00000931864218031089</v>
+        <v>0.00000661763960515794</v>
       </c>
       <c r="D6" t="n">
-        <v>9.66702605941332</v>
+        <v>9.75209706150208</v>
       </c>
       <c r="E6" t="n">
-        <v>0.025089931562785</v>
+        <v>0.026346833492625</v>
       </c>
     </row>
     <row r="7">
@@ -514,16 +495,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0.187327963501053</v>
+        <v>0.182535201939928</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000297201966351602</v>
+        <v>0.000443837133110246</v>
       </c>
       <c r="D7" t="n">
-        <v>16.0138520783649</v>
+        <v>16.1468405563432</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0230385019579785</v>
+        <v>0.0245009715934604</v>
       </c>
     </row>
     <row r="8">
@@ -531,16 +512,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.115783935942083</v>
+        <v>0.0471876279836154</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0000107061006721174</v>
+        <v>0.0945899807933643</v>
       </c>
       <c r="D8" t="n">
-        <v>4.09643111434602</v>
+        <v>4.82570365218177</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0215341921794315</v>
+        <v>0.022941828158057</v>
       </c>
     </row>
     <row r="9">
@@ -548,16 +529,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>0.141975490651403</v>
+        <v>-0.115893350747163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000000000000000000367808469070364</v>
+        <v>0.0000105029022833705</v>
       </c>
       <c r="D9" t="n">
-        <v>1.37307945312407</v>
+        <v>4.09650042413087</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0149022970668485</v>
+        <v>0.0211664164768676</v>
       </c>
     </row>
     <row r="10">
@@ -565,16 +546,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0556759848285457</v>
+        <v>0.140360801571055</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0000632625709914038</v>
+        <v>0.00000000000000000124835135134712</v>
       </c>
       <c r="D10" t="n">
-        <v>1.15242489698422</v>
+        <v>1.38817400364358</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0101165731718879</v>
+        <v>0.0140441203687579</v>
       </c>
     </row>
     <row r="11">
@@ -582,180 +563,33 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0545320923307564</v>
+        <v>-0.0541886414395691</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0300993032838878</v>
+        <v>0.000106753598161196</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8186918125318</v>
+        <v>1.1652324116999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00864634908719147</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+        <v>0.00971648807961164</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.911887413621612</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000211437935794351</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.50912060369293</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.634502122922073</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-0.414070022882029</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000645363556130927</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.5594987924681</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.142581220706782</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="n">
-        <v>-0.450107037807786</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000011934839103628</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.81695577697112</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.12371645945142</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.0480150022711212</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0140246076385798</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.23154370198931</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0382556536940015</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.0675181776433569</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.00334221560885168</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3.08214133761003</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0248025655252418</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.148504083225885</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0000000000000000000053513131703651</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.30340773807415</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.0161697369040743</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.0545521554351314</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.000112277351158584</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.15158151226289</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0103592466917469</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0875657045924108</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0000857878574239824</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.86746701571659</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00961299410466072</v>
+      <c r="B12" t="n">
+        <v>0.056539301121292</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0249987353329278</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.84201712494579</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0079415932391379</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/5. Statistical data analysis/Multiple linear regression/MLR.xlsx
+++ b/Zinc/5. Statistical data analysis/Multiple linear regression/MLR.xlsx
@@ -410,16 +410,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.910695187765478</v>
+        <v>0.926129393360342</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000222900569542897</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407445292713326</v>
       </c>
       <c r="D2" t="n">
-        <v>1.53536661428277</v>
+        <v>1.53468794232318</v>
       </c>
       <c r="E2" t="n">
-        <v>0.606975916550295</v>
+        <v>0.627811922222818</v>
       </c>
     </row>
     <row r="3">
@@ -427,16 +427,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.433260775216521</v>
+        <v>-0.433480863024706</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000262966983851638</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000002348995250765</v>
       </c>
       <c r="D3" t="n">
-        <v>2.52926565538351</v>
+        <v>2.41574452667446</v>
       </c>
       <c r="E3" t="n">
-        <v>0.114612427409943</v>
+        <v>0.106159633885843</v>
       </c>
     </row>
     <row r="4">
@@ -444,16 +444,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.411414098168037</v>
+        <v>-0.388232447015612</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000000000000000000000153137783708475</v>
+        <v>0.00000000000000000000129760820114478</v>
       </c>
       <c r="D4" t="n">
-        <v>9.46344895045439</v>
+        <v>9.12346985271894</v>
       </c>
       <c r="E4" t="n">
-        <v>0.101805360926366</v>
+        <v>0.0963804952953663</v>
       </c>
     </row>
     <row r="5">
@@ -461,16 +461,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.039102431368606</v>
+        <v>-0.0306781682211757</v>
       </c>
       <c r="C5" t="n">
-        <v>0.305847867918413</v>
+        <v>0.403615260024787</v>
       </c>
       <c r="D5" t="n">
-        <v>8.85217301490392</v>
+        <v>8.52210881603353</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0499480437048786</v>
+        <v>0.0472849528339963</v>
       </c>
     </row>
     <row r="6">
@@ -478,16 +478,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.182943297124043</v>
+        <v>-0.105116944474928</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00000661763960515794</v>
+        <v>0.0103853856747688</v>
       </c>
       <c r="D6" t="n">
-        <v>9.75209706150208</v>
+        <v>10.5359812090401</v>
       </c>
       <c r="E6" t="n">
-        <v>0.026346833492625</v>
+        <v>0.0235157874452878</v>
       </c>
     </row>
     <row r="7">
@@ -495,16 +495,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>0.182535201939928</v>
+        <v>0.0788965001548262</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000443837133110246</v>
+        <v>0.153677191547443</v>
       </c>
       <c r="D7" t="n">
-        <v>16.1468405563432</v>
+        <v>19.2786816444938</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0245009715934604</v>
+        <v>0.022195984175227</v>
       </c>
     </row>
     <row r="8">
@@ -512,16 +512,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0471876279836154</v>
+        <v>-0.00434951235588958</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0945899807933643</v>
+        <v>0.872484456559793</v>
       </c>
       <c r="D8" t="n">
-        <v>4.82570365218177</v>
+        <v>4.64287668473474</v>
       </c>
       <c r="E8" t="n">
-        <v>0.022941828158057</v>
+        <v>0.0198299508562585</v>
       </c>
     </row>
     <row r="9">
@@ -529,16 +529,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.115893350747163</v>
+        <v>-0.0542583840178608</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0000105029022833705</v>
+        <v>0.0570085786456517</v>
       </c>
       <c r="D9" t="n">
-        <v>4.09650042413087</v>
+        <v>5.11145222938304</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0211664164768676</v>
+        <v>0.0190055329916806</v>
       </c>
     </row>
     <row r="10">
@@ -546,16 +546,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>0.140360801571055</v>
+        <v>0.171555958972215</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00000000000000000124835135134712</v>
+        <v>0.000000000000000000000000174427624549752</v>
       </c>
       <c r="D10" t="n">
-        <v>1.38817400364358</v>
+        <v>1.4528984885704</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0140441203687579</v>
+        <v>0.0161066567000011</v>
       </c>
     </row>
     <row r="11">
@@ -563,16 +563,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0541886414395691</v>
+        <v>-0.045902911120325</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000106753598161196</v>
+        <v>0.000968206680282881</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1652324116999</v>
+        <v>1.20433858136969</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00971648807961164</v>
+        <v>0.0132772623722509</v>
       </c>
     </row>
     <row r="12">
@@ -580,16 +580,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>0.056539301121292</v>
+        <v>0.0286183582210191</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0249987353329278</v>
+        <v>0.259561121620467</v>
       </c>
       <c r="D12" t="n">
-        <v>3.84201712494579</v>
+        <v>4.06629387395233</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0079415932391379</v>
+        <v>0.00843182122127061</v>
       </c>
     </row>
   </sheetData>
